--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89087488</v>
+        <v>82661531</v>
       </c>
       <c r="B2" t="n">
-        <v>76567</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4194</v>
+        <v>3294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattad jordtunga</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geoglossum cookeianum</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nannf.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ivö, 500 m N om Östergård, Sk</t>
+          <t>betesmark OSO om Ugnsmunnarna, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462448.6306515489</v>
+        <v>462364</v>
       </c>
       <c r="R2" t="n">
-        <v>6219438.378628599</v>
+        <v>6219446</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>bland klippt gräs i mittremsa på markväg</t>
+          <t>naturbetesmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -785,10 +770,838 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Stefan Ekman, Linnea Eide Ekman, Johanna Eide Ekman, Wenche Eide</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113404289</v>
+      </c>
+      <c r="B3" t="n">
+        <v>88978</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3294</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Clavulinopsis corniculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>betesmark OSO om Ugnsmunnarna, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>462452</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6219409</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ivö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stefan Ekman, Wenche Eide</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89087488</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83320</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4194</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Plattad jordtunga</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Geoglossum cookeanum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Minter &amp; P.F.Cannon</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ivö, 500 m N om Östergård, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>462449</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6219438</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ivö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>bland klippt gräs i mittremsa på markväg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Stefan Ekman, Wenche Eide, Linnea Eide Ekman, Johanna Eide Ekman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113404305</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>betesmark OSO om Ugnsmunnarna, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>462452</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6219409</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ivö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stefan Ekman, Wenche Eide</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113404288</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4398</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>betesmark OSO om Ugnsmunnarna, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>462452</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6219409</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ivö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stefan Ekman, Wenche Eide</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>82661561</v>
+      </c>
+      <c r="B7" t="n">
+        <v>82982</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>203889</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Olivjordtunga</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Microglossum olivaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pers.) Gillet</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>betesmark OSO om Ugnsmunnarna, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>462364</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6219446</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ivö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stefan Ekman, Linnea Eide Ekman, Johanna Eide Ekman, Wenche Eide</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113404287</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89060</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>239221</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gliophorus psittacinus var. psittacinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>betesmark OSO om Ugnsmunnarna, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>462452</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6219409</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ivö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Ekman, Wenche Eide</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113404291</v>
+      </c>
+      <c r="B9" t="n">
+        <v>82979</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>259326</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödbrun jordtunga</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Microglossum fuscorubens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Boud.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>betesmark OSO om Ugnsmunnarna, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>462452</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6219409</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ivö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>F-1096932</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stefan Ekman, Wenche Eide</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113404304</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82979</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>259326</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rödbrun jordtunga</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Microglossum fuscorubens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Boud.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>betesmark OSO om Ugnsmunnarna, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>462450</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6219415</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ivö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stefan Ekman, Wenche Eide</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82661531</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113404289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89087488</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113404305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113404288</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82661561</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113404287</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113404291</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,8 +1647,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113404304</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113404288</v>
+        <v>113404287</v>
       </c>
       <c r="B6" t="n">
-        <v>89035</v>
+        <v>89206</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,19 +1120,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4398</v>
+        <v>4393</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Gliophorus psittacinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Herink</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,6 +1188,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,58 +1211,50 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113404288</t>
+          <t>https://artportalen.se/Sighting/113404287</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82661561</v>
+        <v>113404288</v>
       </c>
       <c r="B7" t="n">
-        <v>82982</v>
+        <v>89035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>203889</v>
+        <v>4398</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivjordtunga</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microglossum olivaceum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Pers.) Gillet</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>betesmark OSO om Ugnsmunnarna, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462364</v>
+        <v>462452</v>
       </c>
       <c r="R7" t="n">
-        <v>6219446</v>
+        <v>6219409</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,12 +1278,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,7 +1292,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,51 +1308,64 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Ekman, Linnea Eide Ekman, Johanna Eide Ekman, Wenche Eide</t>
+          <t>Stefan Ekman, Wenche Eide</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82661561</t>
+          <t>https://artportalen.se/Sighting/113404288</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113404287</v>
+        <v>82661561</v>
       </c>
       <c r="B8" t="n">
-        <v>89060</v>
+        <v>82982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>239221</v>
+        <v>203889</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Olivjordtunga</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>Microglossum olivaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.) Gillet</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>betesmark OSO om Ugnsmunnarna, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462452</v>
+        <v>462364</v>
       </c>
       <c r="R8" t="n">
-        <v>6219409</v>
+        <v>6219446</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,13 +1420,13 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Ekman, Wenche Eide</t>
+          <t>Stefan Ekman, Linnea Eide Ekman, Johanna Eide Ekman, Wenche Eide</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113404287</t>
+          <t>https://artportalen.se/Sighting/82661561</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>113404287</v>
       </c>
       <c r="B6" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>113404287</v>
       </c>
       <c r="B6" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>113404287</v>
       </c>
       <c r="B6" t="n">
-        <v>89213</v>
+        <v>89220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>113404287</v>
       </c>
       <c r="B6" t="n">
-        <v>89220</v>
+        <v>89221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>113404287</v>
       </c>
       <c r="B6" t="n">
-        <v>89221</v>
+        <v>89234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62067-2022 artfynd.xlsx
+++ b/artfynd/A 62067-2022 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>113404287</v>
       </c>
       <c r="B6" t="n">
-        <v>89234</v>
+        <v>89235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
